--- a/artfynd/A 8389-2023 artfynd.xlsx
+++ b/artfynd/A 8389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130215881</v>
       </c>
       <c r="B2" t="n">
-        <v>56625</v>
+        <v>56710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130216008</v>
       </c>
       <c r="B3" t="n">
-        <v>56606</v>
+        <v>56691</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>130215905</v>
       </c>
       <c r="B4" t="n">
-        <v>56620</v>
+        <v>56705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>130215976</v>
       </c>
       <c r="B5" t="n">
-        <v>56613</v>
+        <v>56698</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8389-2023 artfynd.xlsx
+++ b/artfynd/A 8389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130215881</v>
       </c>
       <c r="B2" t="n">
-        <v>56710</v>
+        <v>56736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130216008</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>56717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>130215905</v>
       </c>
       <c r="B4" t="n">
-        <v>56705</v>
+        <v>56731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>130215976</v>
       </c>
       <c r="B5" t="n">
-        <v>56698</v>
+        <v>56724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8389-2023 artfynd.xlsx
+++ b/artfynd/A 8389-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130215881</v>
       </c>
       <c r="B2" t="n">
-        <v>56736</v>
+        <v>56738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130216008</v>
       </c>
       <c r="B3" t="n">
-        <v>56717</v>
+        <v>56719</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>130215905</v>
       </c>
       <c r="B4" t="n">
-        <v>56731</v>
+        <v>56733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>130215976</v>
       </c>
       <c r="B5" t="n">
-        <v>56724</v>
+        <v>56726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8389-2023 artfynd.xlsx
+++ b/artfynd/A 8389-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130215881</v>
+        <v>130215905</v>
       </c>
       <c r="B2" t="n">
-        <v>56738</v>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -801,37 +801,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130216008</v>
+        <v>130215976</v>
       </c>
       <c r="B3" t="n">
-        <v>56719</v>
+        <v>56823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -885,22 +885,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130215905</v>
+        <v>130215881</v>
       </c>
       <c r="B4" t="n">
-        <v>56733</v>
+        <v>56835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,26 +938,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1053,37 +1053,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130215976</v>
+        <v>130215997</v>
       </c>
       <c r="B5" t="n">
-        <v>56726</v>
+        <v>56816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/artfynd/A 8389-2023 artfynd.xlsx
+++ b/artfynd/A 8389-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130215905</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130215976</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130215881</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,8 +1196,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130215997</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>